--- a/events/Gyor_2015_MAR/Gyor_2015_MAR_Results.xlsx
+++ b/events/Gyor_2015_MAR/Gyor_2015_MAR_Results.xlsx
@@ -1751,6 +1751,11 @@
           <t>0:11:07.277</t>
         </is>
       </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>64313</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -4673,6 +4678,11 @@
           <t>0:22:30.786</t>
         </is>
       </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>68315</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -5095,6 +5105,11 @@
           <t>0:05:17.445</t>
         </is>
       </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>64338</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -7295,6 +7310,11 @@
           <t>0:10:21.414</t>
         </is>
       </c>
+      <c r="R96" t="inlineStr">
+        <is>
+          <t>48211</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -8082,6 +8102,11 @@
           <t>0:26:29.880</t>
         </is>
       </c>
+      <c r="R107" t="inlineStr">
+        <is>
+          <t>165553</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -8349,6 +8374,11 @@
       <c r="L111" t="n">
         <v>280</v>
       </c>
+      <c r="R111" t="inlineStr">
+        <is>
+          <t>49618</t>
+        </is>
+      </c>
       <c r="X111" t="inlineStr">
         <is>
           <t>DNF</t>
@@ -8477,6 +8507,11 @@
           <t>1:46:46.147</t>
         </is>
       </c>
+      <c r="R113" t="inlineStr">
+        <is>
+          <t>49654</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -9320,6 +9355,11 @@
       <c r="L125" t="n">
         <v>207</v>
       </c>
+      <c r="R125" t="inlineStr">
+        <is>
+          <t>87550</t>
+        </is>
+      </c>
       <c r="X125" t="inlineStr">
         <is>
           <t>DNF</t>
@@ -9387,6 +9427,11 @@
           <t>1:30:20.724</t>
         </is>
       </c>
+      <c r="R126" t="inlineStr">
+        <is>
+          <t>63925</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -10462,6 +10507,11 @@
           <t>0:10:11.346</t>
         </is>
       </c>
+      <c r="R141" t="inlineStr">
+        <is>
+          <t>54039</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -11968,6 +12018,11 @@
           <t>58793</t>
         </is>
       </c>
+      <c r="S162" t="inlineStr">
+        <is>
+          <t>54534</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -12189,6 +12244,11 @@
           <t>0:06:10.938</t>
         </is>
       </c>
+      <c r="R165" t="inlineStr">
+        <is>
+          <t>64313</t>
+        </is>
+      </c>
       <c r="S165" t="inlineStr">
         <is>
           <t>66657</t>
@@ -14379,6 +14439,11 @@
           <t>0:32:00.224</t>
         </is>
       </c>
+      <c r="R195" t="inlineStr">
+        <is>
+          <t>69230</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -14585,6 +14650,11 @@
           <t>0:02:43.668</t>
         </is>
       </c>
+      <c r="R198" t="inlineStr">
+        <is>
+          <t>58775</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -14796,6 +14866,11 @@
           <t>0:09:04.272</t>
         </is>
       </c>
+      <c r="R201" t="inlineStr">
+        <is>
+          <t>135293</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -14863,6 +14938,11 @@
           <t>0:09:32.940</t>
         </is>
       </c>
+      <c r="R202" t="inlineStr">
+        <is>
+          <t>49833</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -15418,6 +15498,11 @@
           <t>2:02:06.732</t>
         </is>
       </c>
+      <c r="R210" t="inlineStr">
+        <is>
+          <t>48400</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -15485,6 +15570,11 @@
           <t>0:00:00.750</t>
         </is>
       </c>
+      <c r="R211" t="inlineStr">
+        <is>
+          <t>49663</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -16776,6 +16866,11 @@
           <t>0:08:44.032</t>
         </is>
       </c>
+      <c r="R229" t="inlineStr">
+        <is>
+          <t>46407</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -16843,6 +16938,11 @@
           <t>0:09:06.657</t>
         </is>
       </c>
+      <c r="R230" t="inlineStr">
+        <is>
+          <t>42348</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -18459,6 +18559,11 @@
           <t>53145</t>
         </is>
       </c>
+      <c r="S254" t="inlineStr">
+        <is>
+          <t>53158</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -18911,6 +19016,11 @@
           <t>61304</t>
         </is>
       </c>
+      <c r="S260" t="inlineStr">
+        <is>
+          <t>62501</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -22236,6 +22346,11 @@
           <t>65440</t>
         </is>
       </c>
+      <c r="S304" t="inlineStr">
+        <is>
+          <t>49833</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -22375,6 +22490,11 @@
           <t>1:54:07.613</t>
         </is>
       </c>
+      <c r="R306" t="inlineStr">
+        <is>
+          <t>49663</t>
+        </is>
+      </c>
       <c r="S306" t="inlineStr">
         <is>
           <t>49664</t>
@@ -22447,6 +22567,11 @@
           <t>0:00:00.563</t>
         </is>
       </c>
+      <c r="R307" t="inlineStr">
+        <is>
+          <t>48400</t>
+        </is>
+      </c>
       <c r="S307" t="inlineStr">
         <is>
           <t>58216</t>
@@ -22827,6 +22952,11 @@
           <t>0:03:06.788</t>
         </is>
       </c>
+      <c r="R312" t="inlineStr">
+        <is>
+          <t>63429</t>
+        </is>
+      </c>
       <c r="S312" t="inlineStr">
         <is>
           <t>49665</t>
@@ -23587,6 +23717,11 @@
           <t>0:09:06.795</t>
         </is>
       </c>
+      <c r="R322" t="inlineStr">
+        <is>
+          <t>61277</t>
+        </is>
+      </c>
       <c r="S322" t="inlineStr">
         <is>
           <t>68207</t>
@@ -24369,6 +24504,11 @@
       </c>
       <c r="L333" t="n">
         <v>705</v>
+      </c>
+      <c r="R333" t="inlineStr">
+        <is>
+          <t>47481</t>
+        </is>
       </c>
       <c r="X333" t="inlineStr">
         <is>
@@ -24509,7 +24649,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D334"/>
+  <dimension ref="A1:D358"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31860,6 +32000,534 @@
         </is>
       </c>
     </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>42348</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>Martin Trebbien Vestergaard</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>LARSEN</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>46407</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>Vitalii</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>TSURKAN</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>47481</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>Rodrigo</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>CAFFA</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>48211</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>Karl Anders</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>SLETSJOEE</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>48400</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>Hank</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>MCGREGOR</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>49618</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>Mads Brandt</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>PEDERSEN</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>49654</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>Levente</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>BALLA</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>49663</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>Adrian</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>BOROS</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>49833</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>Roman</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>ERLINEKOV</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>53158</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>James</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>RUSSELL</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>54039</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>Nick</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>VERDUYCKT</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>54534</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>Annesofie</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>WINTHER</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>58775</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>Nuno</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>BARROS</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>61277</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>Fabio</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>CAMEIRA</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>62501</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>Rasmus</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>MADSEN</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>63429</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>Marton</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>MESZAROS</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>63925</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>Mate</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>GYORGJAKAB</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>64313</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>Donna</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>HUTTON</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>64338</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>David</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>JANIK</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>68315</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>Florencia</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>LLOSA</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>69230</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>Micaela</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>MASLEIN</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>87550</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>Ionel</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>CIORNEI</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>135293</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>Gergely</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>NAGY</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>165553</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>Tsz Chung</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>CHEUNG</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/events/Gyor_2015_MAR/Gyor_2015_MAR_Results.xlsx
+++ b/events/Gyor_2015_MAR/Gyor_2015_MAR_Results.xlsx
@@ -3109,6 +3109,11 @@
           <t>0:13:13.284</t>
         </is>
       </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>76936</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -13151,6 +13156,11 @@
       <c r="Q177" t="inlineStr">
         <is>
           <t>0:02:52.750</t>
+        </is>
+      </c>
+      <c r="R177" t="inlineStr">
+        <is>
+          <t>47779</t>
         </is>
       </c>
     </row>
@@ -24649,7 +24659,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D358"/>
+  <dimension ref="A1:D360"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32528,6 +32538,50 @@
         </is>
       </c>
     </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>76936</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>Anastasiia</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>Ymelianova</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>47779</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>Kristina</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>Bedec</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
